--- a/inventory_updated.xlsx
+++ b/inventory_updated.xlsx
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="K29" s="8" t="n">
-        <v>39.9</v>
+        <v>34.09</v>
       </c>
       <c r="L29" s="8" t="n">
         <v>10</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="K30" s="4" t="n">
-        <v>39.9</v>
+        <v>34.09</v>
       </c>
       <c r="L30" s="4" t="n">
         <v>10</v>
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="K31" s="8" t="n">
-        <v>39.9</v>
+        <v>34.09</v>
       </c>
       <c r="L31" s="8" t="n">
         <v>10</v>
@@ -3219,7 +3219,7 @@
         </is>
       </c>
       <c r="K32" s="4" t="n">
-        <v>39.9</v>
+        <v>34.09</v>
       </c>
       <c r="L32" s="4" t="n">
         <v>10</v>
@@ -3308,7 +3308,7 @@
         </is>
       </c>
       <c r="K33" s="8" t="n">
-        <v>39.9</v>
+        <v>34.09</v>
       </c>
       <c r="L33" s="8" t="n">
         <v>10</v>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="K34" s="4" t="n">
-        <v>39.9</v>
+        <v>34.09</v>
       </c>
       <c r="L34" s="4" t="n">
         <v>10</v>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="K35" s="8" t="n">
-        <v>39.9</v>
+        <v>34.09</v>
       </c>
       <c r="L35" s="8" t="n">
         <v>10</v>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="K36" s="4" t="n">
-        <v>39.9</v>
+        <v>34.09</v>
       </c>
       <c r="L36" s="4" t="n">
         <v>10</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="K37" s="8" t="n">
-        <v>39.9</v>
+        <v>34.09</v>
       </c>
       <c r="L37" s="8" t="n">
         <v>10</v>

--- a/inventory_updated.xlsx
+++ b/inventory_updated.xlsx
@@ -476,10 +476,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U70"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
     <col width="48" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
@@ -6638,6 +6638,807 @@
         <v/>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>RN8-SIL-GN-S-V2</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>Luxury Liquid Silicone Shockproof Case for Realme GT Neo 8 – Skin-Friendly Soft Cube Anti-Drop Protective Back Cover</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>Suitable for Realme Neo8 Mobile Phone Case Realmeneo8 New Model Rmx8899 Protective Cover Gt8 Liquid Silicone</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>Liquid Silicone</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>Mambo Green</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>Realme Neo8</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>https://moveon.global/BD_en/products/0000000AVTXCRWTL-suitable-for-realme-neo8-mobile-phone-case-realmeneo8-new-model-rmx8899-protective-cover-gt8-liquid-silicone/1AD8321207196552</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>Realme Neo8/Liquid Silicone/sku/RN8-SIL-GN-S-V2.jpg</t>
+        </is>
+      </c>
+      <c r="K71" s="8" t="n">
+        <v>268.2</v>
+      </c>
+      <c r="L71" s="8" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="M71" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="N71" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O71" s="8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="P71" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q71" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="8">
+        <f>SUM(K71:Q71)</f>
+        <v/>
+      </c>
+      <c r="S71" s="8">
+        <f>IF(R71&lt;300, R71*1.4, IF(R71&lt;400, R71*1.33, R71*1.25))</f>
+        <v/>
+      </c>
+      <c r="T71" s="9">
+        <f>INT(S71/100)*100 + IF(MOD(ROUND(S71,0),100)&lt;25, 0, IF(MOD(ROUND(S71,0),100)&lt;=74, 49, 99))</f>
+        <v/>
+      </c>
+      <c r="U71" s="8">
+        <f>IF(T71&lt;300, 0, MIN(99, IF(T71&lt;500, T71*7%, IF(T71&lt;700, T71*12%, T71*15%))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>RN8-SIL-YL-S-V2</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Luxury Liquid Silicone Shockproof Case for Realme GT Neo 8 – Skin-Friendly Soft Cube Anti-Drop Protective Back Cover</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Suitable for Realme Neo8 Mobile Phone Case Realmeneo8 New Model Rmx8899 Protective Cover Gt8 Liquid Silicone</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Liquid Silicone</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Cream Yellow</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Realme Neo8</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>https://moveon.global/BD_en/products/0000000AVTXCRWTL-suitable-for-realme-neo8-mobile-phone-case-realmeneo8-new-model-rmx8899-protective-cover-gt8-liquid-silicone/1AD8321207196552</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>Realme Neo8/Liquid Silicone/sku/RN8-SIL-YL-S-V2.jpg</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="n">
+        <v>268.2</v>
+      </c>
+      <c r="L72" s="4" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="M72" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="N72" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O72" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="P72" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" s="4">
+        <f>SUM(K72:Q72)</f>
+        <v/>
+      </c>
+      <c r="S72" s="4">
+        <f>IF(R72&lt;300, R72*1.4, IF(R72&lt;400, R72*1.33, R72*1.25))</f>
+        <v/>
+      </c>
+      <c r="T72" s="5">
+        <f>INT(S72/100)*100 + IF(MOD(ROUND(S72,0),100)&lt;25, 0, IF(MOD(ROUND(S72,0),100)&lt;=74, 49, 99))</f>
+        <v/>
+      </c>
+      <c r="U72" s="4">
+        <f>IF(T72&lt;300, 0, MIN(99, IF(T72&lt;500, T72*7%, IF(T72&lt;700, T72*12%, T72*15%))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>RN8-SIL-PR-S-V2</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Luxury Liquid Silicone Shockproof Case for Realme GT Neo 8 – Skin-Friendly Soft Cube Anti-Drop Protective Back Cover</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Suitable for Realme Neo8 Mobile Phone Case Realmeneo8 New Model Rmx8899 Protective Cover Gt8 Liquid Silicone</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Liquid Silicone</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>Purple Bean</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>Realme Neo8</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>https://moveon.global/BD_en/products/0000000AVTXCRWTL-suitable-for-realme-neo8-mobile-phone-case-realmeneo8-new-model-rmx8899-protective-cover-gt8-liquid-silicone/1AD8321207196552</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>Realme Neo8/Liquid Silicone/sku/RN8-SIL-PR-S-V2.jpg</t>
+        </is>
+      </c>
+      <c r="K73" s="8" t="n">
+        <v>268.2</v>
+      </c>
+      <c r="L73" s="8" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="M73" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="N73" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O73" s="8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="P73" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q73" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" s="8">
+        <f>SUM(K73:Q73)</f>
+        <v/>
+      </c>
+      <c r="S73" s="8">
+        <f>IF(R73&lt;300, R73*1.4, IF(R73&lt;400, R73*1.33, R73*1.25))</f>
+        <v/>
+      </c>
+      <c r="T73" s="9">
+        <f>INT(S73/100)*100 + IF(MOD(ROUND(S73,0),100)&lt;25, 0, IF(MOD(ROUND(S73,0),100)&lt;=74, 49, 99))</f>
+        <v/>
+      </c>
+      <c r="U73" s="8">
+        <f>IF(T73&lt;300, 0, MIN(99, IF(T73&lt;500, T73*7%, IF(T73&lt;700, T73*12%, T73*15%))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>RN8-SIL-PK-S-V2</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Luxury Liquid Silicone Shockproof Case for Realme GT Neo 8 – Skin-Friendly Soft Cube Anti-Drop Protective Back Cover</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Suitable for Realme Neo8 Mobile Phone Case Realmeneo8 New Model Rmx8899 Protective Cover Gt8 Liquid Silicone</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Liquid Silicone</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Sand Pink</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Realme Neo8</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>https://moveon.global/BD_en/products/0000000AVTXCRWTL-suitable-for-realme-neo8-mobile-phone-case-realmeneo8-new-model-rmx8899-protective-cover-gt8-liquid-silicone/1AD8321207196552</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>Realme Neo8/Liquid Silicone/sku/RN8-SIL-PK-S-V2.jpg</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="n">
+        <v>268.2</v>
+      </c>
+      <c r="L74" s="4" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="M74" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="N74" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O74" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="P74" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="4">
+        <f>SUM(K74:Q74)</f>
+        <v/>
+      </c>
+      <c r="S74" s="4">
+        <f>IF(R74&lt;300, R74*1.4, IF(R74&lt;400, R74*1.33, R74*1.25))</f>
+        <v/>
+      </c>
+      <c r="T74" s="5">
+        <f>INT(S74/100)*100 + IF(MOD(ROUND(S74,0),100)&lt;25, 0, IF(MOD(ROUND(S74,0),100)&lt;=74, 49, 99))</f>
+        <v/>
+      </c>
+      <c r="U74" s="4">
+        <f>IF(T74&lt;300, 0, MIN(99, IF(T74&lt;500, T74*7%, IF(T74&lt;700, T74*12%, T74*15%))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>RN8-SIL-BL-S-V2</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Luxury Liquid Silicone Shockproof Case for Realme GT Neo 8 – Skin-Friendly Soft Cube Anti-Drop Protective Back Cover</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>Suitable for Realme Neo8 Mobile Phone Case Realmeneo8 New Model Rmx8899 Protective Cover Gt8 Liquid Silicone</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Liquid Silicone</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>Sky Blue</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>Realme Neo8</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>https://moveon.global/BD_en/products/0000000AVTXCRWTL-suitable-for-realme-neo8-mobile-phone-case-realmeneo8-new-model-rmx8899-protective-cover-gt8-liquid-silicone/1AD8321207196552</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>Realme Neo8/Liquid Silicone/sku/RN8-SIL-BL-S-V2.jpg</t>
+        </is>
+      </c>
+      <c r="K75" s="8" t="n">
+        <v>268.2</v>
+      </c>
+      <c r="L75" s="8" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="M75" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="N75" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O75" s="8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="P75" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q75" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" s="8">
+        <f>SUM(K75:Q75)</f>
+        <v/>
+      </c>
+      <c r="S75" s="8">
+        <f>IF(R75&lt;300, R75*1.4, IF(R75&lt;400, R75*1.33, R75*1.25))</f>
+        <v/>
+      </c>
+      <c r="T75" s="9">
+        <f>INT(S75/100)*100 + IF(MOD(ROUND(S75,0),100)&lt;25, 0, IF(MOD(ROUND(S75,0),100)&lt;=74, 49, 99))</f>
+        <v/>
+      </c>
+      <c r="U75" s="8">
+        <f>IF(T75&lt;300, 0, MIN(99, IF(T75&lt;500, T75*7%, IF(T75&lt;700, T75*12%, T75*15%))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>RN8-SIL-WT-S-V2</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Luxury Liquid Silicone Shockproof Case for Realme GT Neo 8 – Skin-Friendly Soft Cube Anti-Drop Protective Back Cover</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Suitable for Realme Neo8 Mobile Phone Case Realmeneo8 New Model Rmx8899 Protective Cover Gt8 Liquid Silicone</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Liquid Silicone</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Antique White</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Realme Neo8</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>https://moveon.global/BD_en/products/0000000AVTXCRWTL-suitable-for-realme-neo8-mobile-phone-case-realmeneo8-new-model-rmx8899-protective-cover-gt8-liquid-silicone/1AD8321207196552</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>Realme Neo8/Liquid Silicone/sku/RN8-SIL-WT-S-V2.jpg</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="n">
+        <v>268.2</v>
+      </c>
+      <c r="L76" s="4" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="M76" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="N76" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O76" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="P76" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" s="4">
+        <f>SUM(K76:Q76)</f>
+        <v/>
+      </c>
+      <c r="S76" s="4">
+        <f>IF(R76&lt;300, R76*1.4, IF(R76&lt;400, R76*1.33, R76*1.25))</f>
+        <v/>
+      </c>
+      <c r="T76" s="5">
+        <f>INT(S76/100)*100 + IF(MOD(ROUND(S76,0),100)&lt;25, 0, IF(MOD(ROUND(S76,0),100)&lt;=74, 49, 99))</f>
+        <v/>
+      </c>
+      <c r="U76" s="4">
+        <f>IF(T76&lt;300, 0, MIN(99, IF(T76&lt;500, T76*7%, IF(T76&lt;700, T76*12%, T76*15%))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>RN8-SIL-BK-S-V2</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Luxury Liquid Silicone Shockproof Case for Realme GT Neo 8 – Skin-Friendly Soft Cube Anti-Drop Protective Back Cover</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Suitable for Realme Neo8 Mobile Phone Case Realmeneo8 New Model Rmx8899 Protective Cover Gt8 Liquid Silicone</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Liquid Silicone</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>Classic Black</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Realme Neo8</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>https://moveon.global/BD_en/products/0000000AVTXCRWTL-suitable-for-realme-neo8-mobile-phone-case-realmeneo8-new-model-rmx8899-protective-cover-gt8-liquid-silicone/1AD8321207196552</t>
+        </is>
+      </c>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>Realme Neo8/Liquid Silicone/sku/RN8-SIL-BK-S-V2.jpg</t>
+        </is>
+      </c>
+      <c r="K77" s="8" t="n">
+        <v>268.2</v>
+      </c>
+      <c r="L77" s="8" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="M77" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="N77" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O77" s="8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="P77" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q77" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" s="8">
+        <f>SUM(K77:Q77)</f>
+        <v/>
+      </c>
+      <c r="S77" s="8">
+        <f>IF(R77&lt;300, R77*1.4, IF(R77&lt;400, R77*1.33, R77*1.25))</f>
+        <v/>
+      </c>
+      <c r="T77" s="9">
+        <f>INT(S77/100)*100 + IF(MOD(ROUND(S77,0),100)&lt;25, 0, IF(MOD(ROUND(S77,0),100)&lt;=74, 49, 99))</f>
+        <v/>
+      </c>
+      <c r="U77" s="8">
+        <f>IF(T77&lt;300, 0, MIN(99, IF(T77&lt;500, T77*7%, IF(T77&lt;700, T77*12%, T77*15%))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>RN8-SIL-GY-S-V2</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Luxury Liquid Silicone Shockproof Case for Realme GT Neo 8 – Skin-Friendly Soft Cube Anti-Drop Protective Back Cover</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Suitable for Realme Neo8 Mobile Phone Case Realmeneo8 New Model Rmx8899 Protective Cover Gt8 Liquid Silicone</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Liquid Silicone</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Charcoal Gray</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Realme Neo8</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>https://moveon.global/BD_en/products/0000000AVTXCRWTL-suitable-for-realme-neo8-mobile-phone-case-realmeneo8-new-model-rmx8899-protective-cover-gt8-liquid-silicone/1AD8321207196552</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>Realme Neo8/Liquid Silicone/sku/RN8-SIL-GY-S-V2.jpg</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="n">
+        <v>268.2</v>
+      </c>
+      <c r="L78" s="4" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="M78" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="N78" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O78" s="4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="P78" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="4">
+        <f>SUM(K78:Q78)</f>
+        <v/>
+      </c>
+      <c r="S78" s="4">
+        <f>IF(R78&lt;300, R78*1.4, IF(R78&lt;400, R78*1.33, R78*1.25))</f>
+        <v/>
+      </c>
+      <c r="T78" s="5">
+        <f>INT(S78/100)*100 + IF(MOD(ROUND(S78,0),100)&lt;25, 0, IF(MOD(ROUND(S78,0),100)&lt;=74, 49, 99))</f>
+        <v/>
+      </c>
+      <c r="U78" s="4">
+        <f>IF(T78&lt;300, 0, MIN(99, IF(T78&lt;500, T78*7%, IF(T78&lt;700, T78*12%, T78*15%))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>RN8-SIL-WT-S-V3</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Luxury Liquid Silicone Shockproof Case for Realme GT Neo 8 – Skin-Friendly Soft Cube Anti-Drop Protective Back Cover</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Suitable for Realme Neo8 Mobile Phone Case Realmeneo8 New Model Rmx8899 Protective Cover Gt8 Liquid Silicone</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Liquid Silicone</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>Pure White</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>Realme Neo8</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>https://moveon.global/BD_en/products/0000000AVTXCRWTL-suitable-for-realme-neo8-mobile-phone-case-realmeneo8-new-model-rmx8899-protective-cover-gt8-liquid-silicone/1AD8321207196552</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>Realme Neo8/Liquid Silicone/sku/RN8-SIL-WT-S-V3.jpg</t>
+        </is>
+      </c>
+      <c r="K79" s="8" t="n">
+        <v>268.2</v>
+      </c>
+      <c r="L79" s="8" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="M79" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="N79" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="O79" s="8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="P79" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q79" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" s="8">
+        <f>SUM(K79:Q79)</f>
+        <v/>
+      </c>
+      <c r="S79" s="8">
+        <f>IF(R79&lt;300, R79*1.4, IF(R79&lt;400, R79*1.33, R79*1.25))</f>
+        <v/>
+      </c>
+      <c r="T79" s="9">
+        <f>INT(S79/100)*100 + IF(MOD(ROUND(S79,0),100)&lt;25, 0, IF(MOD(ROUND(S79,0),100)&lt;=74, 49, 99))</f>
+        <v/>
+      </c>
+      <c r="U79" s="8">
+        <f>IF(T79&lt;300, 0, MIN(99, IF(T79&lt;500, T79*7%, IF(T79&lt;700, T79*12%, T79*15%))))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
